--- a/rules/CORE-000709/positive/01/data/unit-test-coreid-FB0607-positive.xlsx
+++ b/rules/CORE-000709/positive/01/data/unit-test-coreid-FB0607-positive.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulieChason\GitHub\core-contributor\rules\CORE-000709\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E52FCBC-B0FF-4DE8-BBBA-8BC1A09A577F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5140A628-861C-4BA9-9B2A-234DE6840B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -389,7 +389,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,12 +400,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,33 +460,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -505,14 +499,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -879,402 +867,402 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:26" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:26" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="V2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="Z2" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="A3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z3" s="5" t="s">
+      <c r="P3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>4</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>10</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>10</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>10</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>10</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>10</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>10</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>10</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>1</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>3</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="4">
         <v>10</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="4">
         <v>8</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
         <v>5</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>1</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="4">
         <v>41</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="4">
         <v>22</v>
       </c>
-      <c r="T4" s="5">
+      <c r="T4" s="4">
         <v>8</v>
       </c>
-      <c r="U4" s="5">
+      <c r="U4" s="4">
         <v>28</v>
       </c>
-      <c r="V4" s="5">
+      <c r="V4" s="4">
         <v>8</v>
       </c>
-      <c r="W4" s="5">
+      <c r="W4" s="4">
         <v>28</v>
       </c>
-      <c r="X4" s="5">
+      <c r="X4" s="4">
         <v>14</v>
       </c>
-      <c r="Y4" s="5">
+      <c r="Y4" s="4">
         <v>200</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:26" s="15" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="13">
         <v>1115</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="13">
         <v>701</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="13">
         <v>1948</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="U5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="V5" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="W5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6" t="s">
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1354,82 +1342,83 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:26" s="15" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="13">
         <v>1302</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="13">
         <v>701</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="13">
         <v>1933</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="Q7" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="R7" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="S7" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="T7" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="U7" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="V7" s="6" t="s">
+      <c r="V7" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="W7" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6" t="s">
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12" t="s">
         <v>79</v>
       </c>
     </row>
+    <row r="8" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1441,140 +1430,140 @@
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="A3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="E3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="11">
+      <c r="A4" s="7">
         <v>50</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="7">
         <v>50</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="7">
         <v>50</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="7">
         <v>8</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="7">
         <v>50</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="18"/>
-    </row>
-    <row r="6" spans="1:6" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" t="s">
         <v>105</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="10" t="s">
         <v>108</v>
       </c>
     </row>
